--- a/content_history/pbr-2026-vm20-table-h-i-long-term-spreads.xlsx
+++ b/content_history/pbr-2026-vm20-table-h-i-long-term-spreads.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\PBR\VM20_VM22_ProductSupport\PBR Production Web Data\Current Year\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B97D85E-E831-4AA2-A38C-132ABE3855B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59179775-3BFB-4ECC-81A7-FEFB792FA3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37320" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="March_2026" sheetId="30" r:id="rId1"/>
-    <sheet name="December_2025" sheetId="29" r:id="rId2"/>
-    <sheet name="LEGAL DISCLAIMER" sheetId="4" r:id="rId3"/>
+    <sheet name="June_2026" sheetId="31" r:id="rId1"/>
+    <sheet name="March_2026" sheetId="30" r:id="rId2"/>
+    <sheet name="December_2025" sheetId="29" r:id="rId3"/>
+    <sheet name="LEGAL DISCLAIMER" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="32">
   <si>
     <t>WAL</t>
   </si>
@@ -122,6 +123,12 @@
   </si>
   <si>
     <t>Table I (3/31/2026) Below Investment Grade Long Term Benchmark Spreads (in bps)</t>
+  </si>
+  <si>
+    <t>Table H (6/30/2026) Investment Grade Long Term Benchmark Spreads (in bps)</t>
+  </si>
+  <si>
+    <t>Table I (6/30/2026) Below Investment Grade Long Term Benchmark Spreads (in bps)</t>
   </si>
 </sst>
 </file>
@@ -324,7 +331,7 @@
                   <a14:compatExt spid="_x0000_s1025"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000001040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -645,15 +652,2337 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC69F921-924F-42FD-9921-CFB98B34F709}">
+  <dimension ref="A1:W35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="M1" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="M2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11">
+        <v>2</v>
+      </c>
+      <c r="D3" s="11">
+        <v>3</v>
+      </c>
+      <c r="E3" s="11">
+        <v>4</v>
+      </c>
+      <c r="F3" s="11">
+        <v>5</v>
+      </c>
+      <c r="G3" s="11">
+        <v>6</v>
+      </c>
+      <c r="H3" s="11">
+        <v>7</v>
+      </c>
+      <c r="I3" s="11">
+        <v>8</v>
+      </c>
+      <c r="J3" s="11">
+        <v>9</v>
+      </c>
+      <c r="K3" s="11">
+        <v>10</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="11">
+        <v>11</v>
+      </c>
+      <c r="O3" s="11">
+        <v>12</v>
+      </c>
+      <c r="P3" s="11">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>14</v>
+      </c>
+      <c r="R3" s="11">
+        <v>15</v>
+      </c>
+      <c r="S3" s="11">
+        <v>16</v>
+      </c>
+      <c r="T3" s="11">
+        <v>17</v>
+      </c>
+      <c r="U3" s="11">
+        <v>18</v>
+      </c>
+      <c r="V3" s="11">
+        <v>19</v>
+      </c>
+      <c r="W3" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="T4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="W4" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2">
+        <v>19.41</v>
+      </c>
+      <c r="C5" s="2">
+        <v>27.19</v>
+      </c>
+      <c r="D5" s="2">
+        <v>34.97</v>
+      </c>
+      <c r="E5" s="2">
+        <v>41.73</v>
+      </c>
+      <c r="F5" s="2">
+        <v>48.48</v>
+      </c>
+      <c r="G5" s="2">
+        <v>55.24</v>
+      </c>
+      <c r="H5" s="2">
+        <v>68.86</v>
+      </c>
+      <c r="I5" s="2">
+        <v>82.48</v>
+      </c>
+      <c r="J5" s="2">
+        <v>96.1</v>
+      </c>
+      <c r="K5" s="3">
+        <v>168.92</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O5" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P5" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R5" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S5" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T5" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U5" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V5" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W5" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2">
+        <v>25.01</v>
+      </c>
+      <c r="C6" s="2">
+        <v>33.44</v>
+      </c>
+      <c r="D6" s="2">
+        <v>41.87</v>
+      </c>
+      <c r="E6" s="2">
+        <v>49.45</v>
+      </c>
+      <c r="F6" s="2">
+        <v>57.04</v>
+      </c>
+      <c r="G6" s="2">
+        <v>64.62</v>
+      </c>
+      <c r="H6" s="2">
+        <v>79.510000000000005</v>
+      </c>
+      <c r="I6" s="2">
+        <v>94.4</v>
+      </c>
+      <c r="J6" s="2">
+        <v>109.29</v>
+      </c>
+      <c r="K6" s="3">
+        <v>175.52</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+      <c r="N6" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O6" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P6" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R6" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S6" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T6" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U6" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V6" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W6" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2">
+        <v>30.61</v>
+      </c>
+      <c r="C7" s="2">
+        <v>39.69</v>
+      </c>
+      <c r="D7" s="2">
+        <v>48.77</v>
+      </c>
+      <c r="E7" s="2">
+        <v>57.18</v>
+      </c>
+      <c r="F7" s="2">
+        <v>65.59</v>
+      </c>
+      <c r="G7" s="2">
+        <v>74</v>
+      </c>
+      <c r="H7" s="2">
+        <v>90.16</v>
+      </c>
+      <c r="I7" s="2">
+        <v>106.32</v>
+      </c>
+      <c r="J7" s="2">
+        <v>122.48</v>
+      </c>
+      <c r="K7" s="3">
+        <v>182.12</v>
+      </c>
+      <c r="M7" s="1">
+        <v>3</v>
+      </c>
+      <c r="N7" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O7" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P7" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R7" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S7" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T7" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U7" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V7" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W7" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2">
+        <v>36.21</v>
+      </c>
+      <c r="C8" s="2">
+        <v>45.94</v>
+      </c>
+      <c r="D8" s="2">
+        <v>55.66</v>
+      </c>
+      <c r="E8" s="2">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="F8" s="2">
+        <v>74.14</v>
+      </c>
+      <c r="G8" s="2">
+        <v>83.37</v>
+      </c>
+      <c r="H8" s="2">
+        <v>100.81</v>
+      </c>
+      <c r="I8" s="2">
+        <v>118.24</v>
+      </c>
+      <c r="J8" s="2">
+        <v>135.68</v>
+      </c>
+      <c r="K8" s="3">
+        <v>188.71</v>
+      </c>
+      <c r="M8" s="1">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O8" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P8" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R8" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S8" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T8" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U8" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V8" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W8" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2">
+        <v>42.02</v>
+      </c>
+      <c r="C9" s="2">
+        <v>51.69</v>
+      </c>
+      <c r="D9" s="2">
+        <v>61.36</v>
+      </c>
+      <c r="E9" s="2">
+        <v>71.2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>81.040000000000006</v>
+      </c>
+      <c r="G9" s="2">
+        <v>90.88</v>
+      </c>
+      <c r="H9" s="2">
+        <v>109.55</v>
+      </c>
+      <c r="I9" s="2">
+        <v>128.22</v>
+      </c>
+      <c r="J9" s="2">
+        <v>146.88999999999999</v>
+      </c>
+      <c r="K9" s="3">
+        <v>194.32</v>
+      </c>
+      <c r="M9" s="1">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O9" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P9" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R9" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S9" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T9" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U9" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V9" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W9" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2">
+        <v>47.82</v>
+      </c>
+      <c r="C10" s="2">
+        <v>57.44</v>
+      </c>
+      <c r="D10" s="2">
+        <v>67.05</v>
+      </c>
+      <c r="E10" s="2">
+        <v>77.5</v>
+      </c>
+      <c r="F10" s="2">
+        <v>87.94</v>
+      </c>
+      <c r="G10" s="2">
+        <v>98.38</v>
+      </c>
+      <c r="H10" s="2">
+        <v>118.29</v>
+      </c>
+      <c r="I10" s="2">
+        <v>138.19</v>
+      </c>
+      <c r="J10" s="2">
+        <v>158.1</v>
+      </c>
+      <c r="K10" s="3">
+        <v>199.92</v>
+      </c>
+      <c r="M10" s="1">
+        <v>6</v>
+      </c>
+      <c r="N10" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O10" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P10" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R10" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S10" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T10" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U10" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V10" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W10" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2">
+        <v>53.27</v>
+      </c>
+      <c r="C11" s="2">
+        <v>62.72</v>
+      </c>
+      <c r="D11" s="2">
+        <v>72.17</v>
+      </c>
+      <c r="E11" s="2">
+        <v>82.7</v>
+      </c>
+      <c r="F11" s="2">
+        <v>93.23</v>
+      </c>
+      <c r="G11" s="2">
+        <v>103.76</v>
+      </c>
+      <c r="H11" s="2">
+        <v>123.72</v>
+      </c>
+      <c r="I11" s="2">
+        <v>143.69</v>
+      </c>
+      <c r="J11" s="2">
+        <v>163.65</v>
+      </c>
+      <c r="K11" s="3">
+        <v>202.7</v>
+      </c>
+      <c r="M11" s="1">
+        <v>7</v>
+      </c>
+      <c r="N11" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O11" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P11" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R11" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S11" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T11" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U11" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V11" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W11" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2">
+        <v>58.72</v>
+      </c>
+      <c r="C12" s="2">
+        <v>68.010000000000005</v>
+      </c>
+      <c r="D12" s="2">
+        <v>77.290000000000006</v>
+      </c>
+      <c r="E12" s="2">
+        <v>87.91</v>
+      </c>
+      <c r="F12" s="2">
+        <v>98.52</v>
+      </c>
+      <c r="G12" s="2">
+        <v>109.14</v>
+      </c>
+      <c r="H12" s="2">
+        <v>129.16</v>
+      </c>
+      <c r="I12" s="2">
+        <v>149.18</v>
+      </c>
+      <c r="J12" s="2">
+        <v>169.2</v>
+      </c>
+      <c r="K12" s="3">
+        <v>205.47</v>
+      </c>
+      <c r="M12" s="1">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O12" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P12" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R12" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S12" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T12" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U12" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V12" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W12" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2">
+        <v>64.17</v>
+      </c>
+      <c r="C13" s="2">
+        <v>73.290000000000006</v>
+      </c>
+      <c r="D13" s="2">
+        <v>82.4</v>
+      </c>
+      <c r="E13" s="2">
+        <v>93.11</v>
+      </c>
+      <c r="F13" s="2">
+        <v>103.82</v>
+      </c>
+      <c r="G13" s="2">
+        <v>114.53</v>
+      </c>
+      <c r="H13" s="2">
+        <v>134.6</v>
+      </c>
+      <c r="I13" s="2">
+        <v>154.66999999999999</v>
+      </c>
+      <c r="J13" s="2">
+        <v>174.74</v>
+      </c>
+      <c r="K13" s="3">
+        <v>208.25</v>
+      </c>
+      <c r="M13" s="1">
+        <v>9</v>
+      </c>
+      <c r="N13" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O13" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P13" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R13" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S13" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T13" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U13" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V13" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W13" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2">
+        <v>65.62</v>
+      </c>
+      <c r="C14" s="2">
+        <v>75.08</v>
+      </c>
+      <c r="D14" s="2">
+        <v>84.55</v>
+      </c>
+      <c r="E14" s="2">
+        <v>95.06</v>
+      </c>
+      <c r="F14" s="2">
+        <v>105.58</v>
+      </c>
+      <c r="G14" s="2">
+        <v>116.1</v>
+      </c>
+      <c r="H14" s="2">
+        <v>136.37</v>
+      </c>
+      <c r="I14" s="2">
+        <v>156.63</v>
+      </c>
+      <c r="J14" s="2">
+        <v>176.9</v>
+      </c>
+      <c r="K14" s="3">
+        <v>209.32</v>
+      </c>
+      <c r="M14" s="1">
+        <v>10</v>
+      </c>
+      <c r="N14" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O14" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P14" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R14" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S14" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T14" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U14" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V14" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W14" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2">
+        <v>67.06</v>
+      </c>
+      <c r="C15" s="2">
+        <v>76.88</v>
+      </c>
+      <c r="D15" s="2">
+        <v>86.69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>97.02</v>
+      </c>
+      <c r="F15" s="2">
+        <v>107.34</v>
+      </c>
+      <c r="G15" s="2">
+        <v>117.67</v>
+      </c>
+      <c r="H15" s="2">
+        <v>138.13</v>
+      </c>
+      <c r="I15" s="2">
+        <v>158.6</v>
+      </c>
+      <c r="J15" s="2">
+        <v>179.06</v>
+      </c>
+      <c r="K15" s="3">
+        <v>210.4</v>
+      </c>
+      <c r="M15" s="1">
+        <v>11</v>
+      </c>
+      <c r="N15" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O15" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P15" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R15" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S15" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T15" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U15" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V15" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W15" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2">
+        <v>68.510000000000005</v>
+      </c>
+      <c r="C16" s="2">
+        <v>78.67</v>
+      </c>
+      <c r="D16" s="2">
+        <v>88.83</v>
+      </c>
+      <c r="E16" s="2">
+        <v>98.97</v>
+      </c>
+      <c r="F16" s="2">
+        <v>109.11</v>
+      </c>
+      <c r="G16" s="2">
+        <v>119.25</v>
+      </c>
+      <c r="H16" s="2">
+        <v>139.9</v>
+      </c>
+      <c r="I16" s="2">
+        <v>160.56</v>
+      </c>
+      <c r="J16" s="2">
+        <v>181.21</v>
+      </c>
+      <c r="K16" s="3">
+        <v>211.48</v>
+      </c>
+      <c r="M16" s="1">
+        <v>12</v>
+      </c>
+      <c r="N16" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O16" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P16" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R16" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S16" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T16" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U16" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V16" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W16" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2">
+        <v>69.95</v>
+      </c>
+      <c r="C17" s="2">
+        <v>80.459999999999994</v>
+      </c>
+      <c r="D17" s="2">
+        <v>90.98</v>
+      </c>
+      <c r="E17" s="2">
+        <v>100.92</v>
+      </c>
+      <c r="F17" s="2">
+        <v>110.87</v>
+      </c>
+      <c r="G17" s="2">
+        <v>120.82</v>
+      </c>
+      <c r="H17" s="2">
+        <v>141.66999999999999</v>
+      </c>
+      <c r="I17" s="2">
+        <v>162.52000000000001</v>
+      </c>
+      <c r="J17" s="2">
+        <v>183.37</v>
+      </c>
+      <c r="K17" s="3">
+        <v>212.56</v>
+      </c>
+      <c r="M17" s="1">
+        <v>13</v>
+      </c>
+      <c r="N17" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O17" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P17" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R17" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S17" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T17" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U17" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V17" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W17" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>14</v>
+      </c>
+      <c r="B18" s="2">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="C18" s="2">
+        <v>82.26</v>
+      </c>
+      <c r="D18" s="2">
+        <v>93.12</v>
+      </c>
+      <c r="E18" s="2">
+        <v>102.88</v>
+      </c>
+      <c r="F18" s="2">
+        <v>112.64</v>
+      </c>
+      <c r="G18" s="2">
+        <v>122.39</v>
+      </c>
+      <c r="H18" s="2">
+        <v>143.44</v>
+      </c>
+      <c r="I18" s="2">
+        <v>164.48</v>
+      </c>
+      <c r="J18" s="2">
+        <v>185.53</v>
+      </c>
+      <c r="K18" s="3">
+        <v>213.64</v>
+      </c>
+      <c r="M18" s="1">
+        <v>14</v>
+      </c>
+      <c r="N18" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O18" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P18" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R18" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S18" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T18" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U18" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V18" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W18" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>72.84</v>
+      </c>
+      <c r="C19" s="2">
+        <v>84.05</v>
+      </c>
+      <c r="D19" s="2">
+        <v>95.26</v>
+      </c>
+      <c r="E19" s="2">
+        <v>104.83</v>
+      </c>
+      <c r="F19" s="2">
+        <v>114.4</v>
+      </c>
+      <c r="G19" s="2">
+        <v>123.97</v>
+      </c>
+      <c r="H19" s="2">
+        <v>145.21</v>
+      </c>
+      <c r="I19" s="2">
+        <v>166.44</v>
+      </c>
+      <c r="J19" s="2">
+        <v>187.68</v>
+      </c>
+      <c r="K19" s="3">
+        <v>214.72</v>
+      </c>
+      <c r="M19" s="1">
+        <v>15</v>
+      </c>
+      <c r="N19" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O19" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P19" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R19" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S19" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T19" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U19" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V19" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W19" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>74.290000000000006</v>
+      </c>
+      <c r="C20" s="2">
+        <v>85.85</v>
+      </c>
+      <c r="D20" s="2">
+        <v>97.41</v>
+      </c>
+      <c r="E20" s="2">
+        <v>106.79</v>
+      </c>
+      <c r="F20" s="2">
+        <v>116.16</v>
+      </c>
+      <c r="G20" s="2">
+        <v>125.54</v>
+      </c>
+      <c r="H20" s="2">
+        <v>146.97</v>
+      </c>
+      <c r="I20" s="2">
+        <v>168.41</v>
+      </c>
+      <c r="J20" s="2">
+        <v>189.84</v>
+      </c>
+      <c r="K20" s="3">
+        <v>215.79</v>
+      </c>
+      <c r="M20" s="1">
+        <v>16</v>
+      </c>
+      <c r="N20" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O20" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P20" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R20" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S20" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T20" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U20" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V20" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W20" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>75.73</v>
+      </c>
+      <c r="C21" s="2">
+        <v>87.64</v>
+      </c>
+      <c r="D21" s="2">
+        <v>99.55</v>
+      </c>
+      <c r="E21" s="2">
+        <v>108.74</v>
+      </c>
+      <c r="F21" s="2">
+        <v>117.93</v>
+      </c>
+      <c r="G21" s="2">
+        <v>127.12</v>
+      </c>
+      <c r="H21" s="2">
+        <v>148.74</v>
+      </c>
+      <c r="I21" s="2">
+        <v>170.37</v>
+      </c>
+      <c r="J21" s="2">
+        <v>191.99</v>
+      </c>
+      <c r="K21" s="3">
+        <v>216.87</v>
+      </c>
+      <c r="M21" s="1">
+        <v>17</v>
+      </c>
+      <c r="N21" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O21" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P21" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R21" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S21" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T21" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U21" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V21" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W21" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>77.17</v>
+      </c>
+      <c r="C22" s="2">
+        <v>89.43</v>
+      </c>
+      <c r="D22" s="2">
+        <v>101.7</v>
+      </c>
+      <c r="E22" s="2">
+        <v>110.69</v>
+      </c>
+      <c r="F22" s="2">
+        <v>119.69</v>
+      </c>
+      <c r="G22" s="2">
+        <v>128.69</v>
+      </c>
+      <c r="H22" s="2">
+        <v>150.51</v>
+      </c>
+      <c r="I22" s="2">
+        <v>172.33</v>
+      </c>
+      <c r="J22" s="2">
+        <v>194.15</v>
+      </c>
+      <c r="K22" s="3">
+        <v>217.95</v>
+      </c>
+      <c r="M22" s="1">
+        <v>18</v>
+      </c>
+      <c r="N22" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O22" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P22" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R22" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S22" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T22" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U22" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V22" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W22" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>78.62</v>
+      </c>
+      <c r="C23" s="2">
+        <v>91.23</v>
+      </c>
+      <c r="D23" s="2">
+        <v>103.84</v>
+      </c>
+      <c r="E23" s="2">
+        <v>112.65</v>
+      </c>
+      <c r="F23" s="2">
+        <v>121.46</v>
+      </c>
+      <c r="G23" s="2">
+        <v>130.26</v>
+      </c>
+      <c r="H23" s="2">
+        <v>152.28</v>
+      </c>
+      <c r="I23" s="2">
+        <v>174.29</v>
+      </c>
+      <c r="J23" s="2">
+        <v>196.31</v>
+      </c>
+      <c r="K23" s="3">
+        <v>219.03</v>
+      </c>
+      <c r="M23" s="1">
+        <v>19</v>
+      </c>
+      <c r="N23" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O23" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P23" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R23" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S23" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T23" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U23" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V23" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W23" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <v>80.06</v>
+      </c>
+      <c r="C24" s="2">
+        <v>93.02</v>
+      </c>
+      <c r="D24" s="2">
+        <v>105.98</v>
+      </c>
+      <c r="E24" s="2">
+        <v>114.6</v>
+      </c>
+      <c r="F24" s="2">
+        <v>123.22</v>
+      </c>
+      <c r="G24" s="2">
+        <v>131.84</v>
+      </c>
+      <c r="H24" s="2">
+        <v>154.05000000000001</v>
+      </c>
+      <c r="I24" s="2">
+        <v>176.25</v>
+      </c>
+      <c r="J24" s="2">
+        <v>198.46</v>
+      </c>
+      <c r="K24" s="3">
+        <v>220.11</v>
+      </c>
+      <c r="M24" s="1">
+        <v>20</v>
+      </c>
+      <c r="N24" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O24" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P24" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R24" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S24" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T24" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U24" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V24" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W24" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>81.510000000000005</v>
+      </c>
+      <c r="C25" s="2">
+        <v>94.82</v>
+      </c>
+      <c r="D25" s="2">
+        <v>108.13</v>
+      </c>
+      <c r="E25" s="2">
+        <v>116.55</v>
+      </c>
+      <c r="F25" s="2">
+        <v>124.98</v>
+      </c>
+      <c r="G25" s="2">
+        <v>133.41</v>
+      </c>
+      <c r="H25" s="2">
+        <v>155.81</v>
+      </c>
+      <c r="I25" s="2">
+        <v>178.22</v>
+      </c>
+      <c r="J25" s="2">
+        <v>200.62</v>
+      </c>
+      <c r="K25" s="3">
+        <v>221.18</v>
+      </c>
+      <c r="M25" s="1">
+        <v>21</v>
+      </c>
+      <c r="N25" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O25" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P25" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R25" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S25" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T25" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U25" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V25" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W25" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2">
+        <v>82.95</v>
+      </c>
+      <c r="C26" s="2">
+        <v>96.61</v>
+      </c>
+      <c r="D26" s="2">
+        <v>110.27</v>
+      </c>
+      <c r="E26" s="2">
+        <v>118.51</v>
+      </c>
+      <c r="F26" s="2">
+        <v>126.75</v>
+      </c>
+      <c r="G26" s="2">
+        <v>134.97999999999999</v>
+      </c>
+      <c r="H26" s="2">
+        <v>157.58000000000001</v>
+      </c>
+      <c r="I26" s="2">
+        <v>180.18</v>
+      </c>
+      <c r="J26" s="2">
+        <v>202.77</v>
+      </c>
+      <c r="K26" s="3">
+        <v>222.26</v>
+      </c>
+      <c r="M26" s="1">
+        <v>22</v>
+      </c>
+      <c r="N26" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O26" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P26" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R26" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S26" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T26" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U26" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V26" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W26" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>84.4</v>
+      </c>
+      <c r="C27" s="2">
+        <v>98.41</v>
+      </c>
+      <c r="D27" s="2">
+        <v>112.41</v>
+      </c>
+      <c r="E27" s="2">
+        <v>120.46</v>
+      </c>
+      <c r="F27" s="2">
+        <v>128.51</v>
+      </c>
+      <c r="G27" s="2">
+        <v>136.56</v>
+      </c>
+      <c r="H27" s="2">
+        <v>159.35</v>
+      </c>
+      <c r="I27" s="2">
+        <v>182.14</v>
+      </c>
+      <c r="J27" s="2">
+        <v>204.93</v>
+      </c>
+      <c r="K27" s="3">
+        <v>223.34</v>
+      </c>
+      <c r="M27" s="1">
+        <v>23</v>
+      </c>
+      <c r="N27" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O27" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P27" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R27" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S27" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T27" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U27" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V27" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W27" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2">
+        <v>85.84</v>
+      </c>
+      <c r="C28" s="2">
+        <v>100.2</v>
+      </c>
+      <c r="D28" s="2">
+        <v>114.56</v>
+      </c>
+      <c r="E28" s="2">
+        <v>122.42</v>
+      </c>
+      <c r="F28" s="2">
+        <v>130.27000000000001</v>
+      </c>
+      <c r="G28" s="2">
+        <v>138.13</v>
+      </c>
+      <c r="H28" s="2">
+        <v>161.12</v>
+      </c>
+      <c r="I28" s="2">
+        <v>184.1</v>
+      </c>
+      <c r="J28" s="2">
+        <v>207.09</v>
+      </c>
+      <c r="K28" s="3">
+        <v>224.42</v>
+      </c>
+      <c r="M28" s="1">
+        <v>24</v>
+      </c>
+      <c r="N28" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O28" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P28" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R28" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S28" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T28" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U28" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V28" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W28" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>87.29</v>
+      </c>
+      <c r="C29" s="2">
+        <v>101.99</v>
+      </c>
+      <c r="D29" s="2">
+        <v>116.7</v>
+      </c>
+      <c r="E29" s="2">
+        <v>124.37</v>
+      </c>
+      <c r="F29" s="2">
+        <v>132.04</v>
+      </c>
+      <c r="G29" s="2">
+        <v>139.71</v>
+      </c>
+      <c r="H29" s="2">
+        <v>162.88999999999999</v>
+      </c>
+      <c r="I29" s="2">
+        <v>186.06</v>
+      </c>
+      <c r="J29" s="2">
+        <v>209.24</v>
+      </c>
+      <c r="K29" s="3">
+        <v>225.5</v>
+      </c>
+      <c r="M29" s="1">
+        <v>25</v>
+      </c>
+      <c r="N29" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O29" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P29" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R29" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S29" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T29" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U29" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V29" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W29" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2">
+        <v>88.73</v>
+      </c>
+      <c r="C30" s="2">
+        <v>103.79</v>
+      </c>
+      <c r="D30" s="2">
+        <v>118.85</v>
+      </c>
+      <c r="E30" s="2">
+        <v>126.32</v>
+      </c>
+      <c r="F30" s="2">
+        <v>133.80000000000001</v>
+      </c>
+      <c r="G30" s="2">
+        <v>141.28</v>
+      </c>
+      <c r="H30" s="2">
+        <v>164.65</v>
+      </c>
+      <c r="I30" s="2">
+        <v>188.03</v>
+      </c>
+      <c r="J30" s="2">
+        <v>211.4</v>
+      </c>
+      <c r="K30" s="3">
+        <v>226.57</v>
+      </c>
+      <c r="M30" s="1">
+        <v>26</v>
+      </c>
+      <c r="N30" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O30" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P30" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R30" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S30" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T30" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U30" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V30" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W30" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2">
+        <v>90.17</v>
+      </c>
+      <c r="C31" s="2">
+        <v>105.58</v>
+      </c>
+      <c r="D31" s="2">
+        <v>120.99</v>
+      </c>
+      <c r="E31" s="2">
+        <v>128.28</v>
+      </c>
+      <c r="F31" s="2">
+        <v>135.57</v>
+      </c>
+      <c r="G31" s="2">
+        <v>142.85</v>
+      </c>
+      <c r="H31" s="2">
+        <v>166.42</v>
+      </c>
+      <c r="I31" s="2">
+        <v>189.99</v>
+      </c>
+      <c r="J31" s="2">
+        <v>213.56</v>
+      </c>
+      <c r="K31" s="3">
+        <v>227.65</v>
+      </c>
+      <c r="M31" s="1">
+        <v>27</v>
+      </c>
+      <c r="N31" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O31" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P31" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R31" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S31" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T31" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U31" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V31" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W31" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2">
+        <v>91.62</v>
+      </c>
+      <c r="C32" s="2">
+        <v>107.38</v>
+      </c>
+      <c r="D32" s="2">
+        <v>123.13</v>
+      </c>
+      <c r="E32" s="2">
+        <v>130.22999999999999</v>
+      </c>
+      <c r="F32" s="2">
+        <v>137.33000000000001</v>
+      </c>
+      <c r="G32" s="2">
+        <v>144.43</v>
+      </c>
+      <c r="H32" s="2">
+        <v>168.19</v>
+      </c>
+      <c r="I32" s="2">
+        <v>191.95</v>
+      </c>
+      <c r="J32" s="2">
+        <v>215.71</v>
+      </c>
+      <c r="K32" s="3">
+        <v>228.73</v>
+      </c>
+      <c r="M32" s="1">
+        <v>28</v>
+      </c>
+      <c r="N32" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O32" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P32" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R32" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S32" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T32" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U32" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V32" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W32" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2">
+        <v>93.06</v>
+      </c>
+      <c r="C33" s="2">
+        <v>109.17</v>
+      </c>
+      <c r="D33" s="2">
+        <v>125.28</v>
+      </c>
+      <c r="E33" s="2">
+        <v>132.18</v>
+      </c>
+      <c r="F33" s="2">
+        <v>139.09</v>
+      </c>
+      <c r="G33" s="2">
+        <v>146</v>
+      </c>
+      <c r="H33" s="2">
+        <v>169.96</v>
+      </c>
+      <c r="I33" s="2">
+        <v>193.91</v>
+      </c>
+      <c r="J33" s="2">
+        <v>217.87</v>
+      </c>
+      <c r="K33" s="3">
+        <v>229.81</v>
+      </c>
+      <c r="M33" s="1">
+        <v>29</v>
+      </c>
+      <c r="N33" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O33" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P33" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R33" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S33" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T33" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U33" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V33" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W33" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>30</v>
+      </c>
+      <c r="B34" s="2">
+        <v>94.51</v>
+      </c>
+      <c r="C34" s="2">
+        <v>110.96</v>
+      </c>
+      <c r="D34" s="2">
+        <v>127.42</v>
+      </c>
+      <c r="E34" s="2">
+        <v>134.13999999999999</v>
+      </c>
+      <c r="F34" s="2">
+        <v>140.86000000000001</v>
+      </c>
+      <c r="G34" s="2">
+        <v>147.58000000000001</v>
+      </c>
+      <c r="H34" s="2">
+        <v>171.72</v>
+      </c>
+      <c r="I34" s="2">
+        <v>195.87</v>
+      </c>
+      <c r="J34" s="2">
+        <v>220.02</v>
+      </c>
+      <c r="K34" s="3">
+        <v>230.89</v>
+      </c>
+      <c r="M34" s="1">
+        <v>30</v>
+      </c>
+      <c r="N34" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O34" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="P34" s="3">
+        <v>352.74</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>408.23</v>
+      </c>
+      <c r="R34" s="3">
+        <v>463.73</v>
+      </c>
+      <c r="S34" s="3">
+        <v>628.41999999999996</v>
+      </c>
+      <c r="T34" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U34" s="3">
+        <v>957.82</v>
+      </c>
+      <c r="V34" s="3">
+        <v>1122.51</v>
+      </c>
+      <c r="W34" s="3">
+        <v>1287.21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="2">
+        <v>68.619</v>
+      </c>
+      <c r="C35" s="2">
+        <v>80.429666666666677</v>
+      </c>
+      <c r="D35" s="2">
+        <v>92.239666666666665</v>
+      </c>
+      <c r="E35" s="2">
+        <v>101.07633333333334</v>
+      </c>
+      <c r="F35" s="2">
+        <v>109.91333333333337</v>
+      </c>
+      <c r="G35" s="2">
+        <v>118.75</v>
+      </c>
+      <c r="H35" s="2">
+        <v>139.65400000000002</v>
+      </c>
+      <c r="I35" s="2">
+        <v>160.55733333333328</v>
+      </c>
+      <c r="J35" s="2">
+        <v>181.46133333333333</v>
+      </c>
+      <c r="K35" s="2">
+        <v>211.60499999999999</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N35" s="3">
+        <v>241.75</v>
+      </c>
+      <c r="O35" s="3">
+        <v>297.23999999999984</v>
+      </c>
+      <c r="P35" s="3">
+        <v>352.73999999999984</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>408.22999999999973</v>
+      </c>
+      <c r="R35" s="3">
+        <v>463.72999999999968</v>
+      </c>
+      <c r="S35" s="3">
+        <v>628.41999999999985</v>
+      </c>
+      <c r="T35" s="3">
+        <v>793.12</v>
+      </c>
+      <c r="U35" s="3">
+        <v>957.81999999999982</v>
+      </c>
+      <c r="V35" s="3">
+        <v>1122.5099999999993</v>
+      </c>
+      <c r="W35" s="3">
+        <v>1287.2099999999994</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="N2:W2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{071A1AF5-A164-49E6-889A-F25D30A933DF}">
   <dimension ref="A1:W35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.08984375" customWidth="1"/>
-    <col min="13" max="13" width="11.08984375" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>28</v>
       </c>
@@ -681,7 +3010,7 @@
       <c r="V1" s="9"/>
       <c r="W1" s="9"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -713,7 +3042,7 @@
       <c r="V2" s="12"/>
       <c r="W2" s="12"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
@@ -781,7 +3110,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
@@ -849,7 +3178,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -917,7 +3246,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -985,7 +3314,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1053,7 +3382,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1121,7 +3450,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1189,7 +3518,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1257,7 +3586,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1325,7 +3654,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1393,7 +3722,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1461,7 +3790,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1529,7 +3858,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1597,7 +3926,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1665,7 +3994,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1733,7 +4062,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -1801,7 +4130,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -1869,7 +4198,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -1937,7 +4266,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -2005,7 +4334,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -2073,7 +4402,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -2141,7 +4470,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -2209,7 +4538,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -2277,7 +4606,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -2345,7 +4674,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -2413,7 +4742,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -2481,7 +4810,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -2549,7 +4878,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -2617,7 +4946,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -2685,7 +5014,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -2753,7 +5082,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -2821,7 +5150,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -2889,7 +5218,7 @@
         <v>1286.95</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>12</v>
       </c>
@@ -2966,17 +5295,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73BF4DDD-FF0B-4F49-A7AA-1582BBDA098E}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:W35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" customWidth="1"/>
-    <col min="13" max="13" width="11.1796875" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>26</v>
       </c>
@@ -3004,7 +5333,7 @@
       <c r="V1" s="9"/>
       <c r="W1" s="9"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -3036,7 +5365,7 @@
       <c r="V2" s="12"/>
       <c r="W2" s="12"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
@@ -3104,7 +5433,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
@@ -3172,7 +5501,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3240,7 +5569,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -3308,7 +5637,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -3376,7 +5705,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -3444,7 +5773,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -3512,7 +5841,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -3580,7 +5909,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -3648,7 +5977,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -3716,7 +6045,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -3784,7 +6113,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -3852,7 +6181,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -3920,7 +6249,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -3988,7 +6317,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -4056,7 +6385,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -4124,7 +6453,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -4192,7 +6521,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -4260,7 +6589,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -4328,7 +6657,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -4396,7 +6725,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -4464,7 +6793,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -4532,7 +6861,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -4600,7 +6929,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -4668,7 +6997,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -4736,7 +7065,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -4804,7 +7133,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -4872,7 +7201,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -4940,7 +7269,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -5008,7 +7337,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -5076,7 +7405,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -5144,7 +7473,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -5212,7 +7541,7 @@
         <v>1284.47</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>12</v>
       </c>
@@ -5289,13 +7618,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <sheetProtection password="9690" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
